--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.96071448969072</v>
+        <v>4.543616104574743</v>
       </c>
       <c r="D2" t="n">
-        <v>28.37449993258448</v>
+        <v>4.610856239044978</v>
       </c>
       <c r="E2" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F2" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.97858731983999</v>
+        <v>6.334020439473998</v>
       </c>
       <c r="D3" t="n">
-        <v>5.852349955359813</v>
+        <v>0.9510068677459697</v>
       </c>
       <c r="E3" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F3" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.97712903769359</v>
+        <v>9.258783468625207</v>
       </c>
       <c r="D4" t="n">
-        <v>17.44276354251241</v>
+        <v>2.834449075658267</v>
       </c>
       <c r="E4" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F4" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.27873932954496</v>
+        <v>8.170295141051056</v>
       </c>
       <c r="D5" t="n">
-        <v>11.40175425099138</v>
+        <v>1.852785065786099</v>
       </c>
       <c r="E5" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F5" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.74090697814047</v>
+        <v>8.895397383947827</v>
       </c>
       <c r="D6" t="n">
-        <v>21.94202301415475</v>
+        <v>3.565578739800147</v>
       </c>
       <c r="E6" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F6" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.89061023678845</v>
+        <v>10.54472416347812</v>
       </c>
       <c r="D7" t="n">
-        <v>34.03347399052176</v>
+        <v>5.530439523459785</v>
       </c>
       <c r="E7" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F7" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76.89566294296884</v>
+        <v>12.49554522823244</v>
       </c>
       <c r="D8" t="n">
-        <v>41.69232543286594</v>
+        <v>6.775002882840715</v>
       </c>
       <c r="E8" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F8" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>93.64241932167123</v>
+        <v>15.21689313977157</v>
       </c>
       <c r="D9" t="n">
-        <v>92.75578116024462</v>
+        <v>15.07281443853975</v>
       </c>
       <c r="E9" t="n">
-        <v>19.39829452384054</v>
+        <v>3.152222860124088</v>
       </c>
       <c r="F9" t="n">
-        <v>25.55084233666797</v>
+        <v>4.152011879708545</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
